--- a/assets/constructions/examples/ctd_met.xlsx
+++ b/assets/constructions/examples/ctd_met.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,36 +624,61 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GS6C2001015-L35R00VTH</t>
+          <t>E-TSL20.006026080-T4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>AMATI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GM Solid</t>
+          <t>E-TSL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PMKNS</t>
+          <t>PMK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>HA-10</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -675,23 +700,25 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>9.9</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q2" t="n">
         <v>10</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="W2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
@@ -706,17 +733,15 @@
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="n">
-        <v>2</v>
-      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>VTH</t>
+          <t>Super MG</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>TISIN</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
@@ -740,7 +765,26 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2021/Groovex VARGUS</t>
+          <t>2023/Amati Форма Точности</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1647.36</v>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>20230.57</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>PMK</t>
         </is>
       </c>
     </row>
@@ -862,36 +906,53 @@
           <t>2023/Amati Форма Точности</t>
         </is>
       </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1389.44</v>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>17063.16</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E-TSL18.006026080-T4</t>
+          <t>MB8.0150.00-25/AL41</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AMATI</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>E-TSL</t>
-        </is>
-      </c>
+          <t>DUEMMEL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PMK</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>HA-18</t>
+          <t>HB-8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -913,30 +974,30 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>18</v>
+        <v>7.8</v>
       </c>
       <c r="P4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="W4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -946,15 +1007,17 @@
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>2</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Super MG</t>
+          <t>AL41</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>TISIN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
@@ -978,14 +1041,33 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2023/Amati Форма Точности</t>
+          <t>2019/PRODUCT OVERVIEW.pdf</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>146.02</v>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>13424.16</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E-TSL16.001021080-T4</t>
+          <t>E-TSL20.002022080-T4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1005,12 +1087,12 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>HA-16</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,16 +1114,16 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1100,36 +1182,55 @@
           <t>2023/Amati Форма Точности</t>
         </is>
       </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1647.36</v>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>20230.57</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E-TSL12.004014075-T4</t>
+          <t>GS4C1000812-L25R00VTH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMATI</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>E-TSL</t>
+          <t>GM Solid</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PMK</t>
+          <t>PMKNS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>HA-12</t>
+          <t>HA-8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1151,22 +1252,20 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>7.9</v>
       </c>
       <c r="P6" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>6</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="W6" t="n">
         <v>4</v>
@@ -1184,15 +1283,17 @@
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Super MG</t>
+          <t>VTH</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>TISIN</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr"/>
@@ -1216,7 +1317,26 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2023/Amati Форма Точности</t>
+          <t>2021/Groovex VARGUS</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>104.13</v>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>9573.059999999999</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
